--- a/Pooja Oil Catalogue.xlsx
+++ b/Pooja Oil Catalogue.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{7C5AD52C-367D-4751-80B7-8CB77532D2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D6154F5-F1F0-41FB-BFE7-5B782CC26B0F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFC2897-39EF-447C-B161-7796E6D237B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{988DBE6C-EE94-47FA-8870-2C94BA4EE1E9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Category</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pooja Samagri </t>
+  </si>
+  <si>
+    <t>HEM Gangajal</t>
   </si>
 </sst>
 </file>
@@ -243,10 +246,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -595,7 +594,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">

--- a/Pooja Oil Catalogue.xlsx
+++ b/Pooja Oil Catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFC2897-39EF-447C-B161-7796E6D237B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F591F7-9059-417B-9163-54AF80EA0FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{988DBE6C-EE94-47FA-8870-2C94BA4EE1E9}"/>
   </bookViews>
@@ -134,15 +134,9 @@
     <t>Madhur Guggal Cup Dhoop (Mrp)</t>
   </si>
   <si>
-    <t xml:space="preserve"> Cup Dhoop </t>
-  </si>
-  <si>
     <t xml:space="preserve">HEM  Camphor </t>
   </si>
   <si>
-    <t xml:space="preserve"> Pooja Oil </t>
-  </si>
-  <si>
     <t>Ghee Diya</t>
   </si>
   <si>
@@ -150,6 +144,12 @@
   </si>
   <si>
     <t>HEM Gangajal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooja Oil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cup Dhoop </t>
   </si>
 </sst>
 </file>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -231,6 +231,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +573,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.36328125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.08984375" bestFit="1" customWidth="1"/>
@@ -576,7 +581,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -593,175 +598,178 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>35</v>
+      <c r="A3" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>33</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>33</v>
+      <c r="A5" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>34</v>
+      <c r="A8" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>34</v>
+      <c r="A9" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>34</v>
+      <c r="A10" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="2" t="s">
-        <v>13</v>
+      <c r="C11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
+      <c r="A12" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
+      <c r="A13" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
+      <c r="A14" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E14" s="4"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E14">
+    <sortCondition ref="A1:A14"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Pooja Oil Catalogue.xlsx
+++ b/Pooja Oil Catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F591F7-9059-417B-9163-54AF80EA0FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B8594-ED62-40CE-836A-D161977FD911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{988DBE6C-EE94-47FA-8870-2C94BA4EE1E9}"/>
   </bookViews>
